--- a/tests/fixtures/bridge_bkup.xlsx
+++ b/tests/fixtures/bridge_bkup.xlsx
@@ -8,13 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\MyPy\Packages\fltk\tests\fixtures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8158670D-ADD5-4EA4-8607-C6A2C631FF89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B962AED8-AFCD-407C-BC85-ED37BD22630D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8985" yWindow="4185" windowWidth="28800" windowHeight="11295" xr2:uid="{55D8B766-AA58-4EC0-B6FD-8EEF6CA6A6EF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{55D8B766-AA58-4EC0-B6FD-8EEF6CA6A6EF}"/>
   </bookViews>
   <sheets>
     <sheet name="data1" sheetId="7" r:id="rId1"/>
-    <sheet name="concepts_ratios" sheetId="5" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -52,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="30">
   <si>
     <t>DirectLabor</t>
   </si>
@@ -133,6 +132,15 @@
   </si>
   <si>
     <t>den</t>
+  </si>
+  <si>
+    <t>q2020-3</t>
+  </si>
+  <si>
+    <t>q2020-4</t>
+  </si>
+  <si>
+    <t>q2020-5</t>
   </si>
 </sst>
 </file>
@@ -143,12 +151,6 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -173,8 +175,16 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF0070C0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -217,6 +227,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -244,24 +260,28 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -577,7 +597,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A61EEF6B-52C6-492C-B13D-8396A5497842}">
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:L49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="6" width="30.7109375" customWidth="1"/>
@@ -637,9 +657,11 @@
         <v>0.13043478260869565</v>
       </c>
       <c r="H2">
+        <f>H3</f>
         <v>150</v>
       </c>
       <c r="I2">
+        <f>I4</f>
         <v>1150</v>
       </c>
     </row>
@@ -666,10 +688,11 @@
         <f>H3 / I3</f>
         <v>0.15</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="10">
         <v>150</v>
       </c>
       <c r="I3">
+        <f>H4</f>
         <v>1000</v>
       </c>
     </row>
@@ -696,10 +719,10 @@
         <f>H4 / I4</f>
         <v>0.86956521739130432</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="10">
         <v>1000</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="10">
         <v>1150</v>
       </c>
     </row>
@@ -727,9 +750,11 @@
         <v>5.7142857142857144</v>
       </c>
       <c r="H5">
+        <f>H6</f>
         <v>1000</v>
       </c>
       <c r="I5">
+        <f>I7</f>
         <v>175</v>
       </c>
     </row>
@@ -756,10 +781,11 @@
         <f t="shared" ref="G6:G13" si="0">H6 / I6</f>
         <v>3.3333333333333335</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="10">
         <v>1000</v>
       </c>
       <c r="I6">
+        <f>H7</f>
         <v>300</v>
       </c>
     </row>
@@ -786,10 +812,10 @@
         <f t="shared" si="0"/>
         <v>1.7142857142857142</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="10">
         <v>300</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="10">
         <v>175</v>
       </c>
     </row>
@@ -817,9 +843,11 @@
         <v>0.12</v>
       </c>
       <c r="H8">
+        <f>H9</f>
         <v>120</v>
       </c>
       <c r="I8">
+        <f>I10</f>
         <v>1000</v>
       </c>
     </row>
@@ -846,10 +874,11 @@
         <f t="shared" si="0"/>
         <v>0.10909090909090909</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="10">
         <v>120</v>
       </c>
       <c r="I9">
+        <f>H10</f>
         <v>1100</v>
       </c>
     </row>
@@ -876,10 +905,10 @@
         <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="10">
         <v>1100</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="10">
         <v>1000</v>
       </c>
     </row>
@@ -907,9 +936,11 @@
         <v>6.875</v>
       </c>
       <c r="H11">
+        <f>H12</f>
         <v>275</v>
       </c>
       <c r="I11">
+        <f>I13</f>
         <v>40</v>
       </c>
     </row>
@@ -936,10 +967,11 @@
         <f t="shared" si="0"/>
         <v>5.5</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="10">
         <v>275</v>
       </c>
       <c r="I12">
+        <f>H13</f>
         <v>50</v>
       </c>
     </row>
@@ -966,10 +998,10 @@
         <f t="shared" si="0"/>
         <v>1.25</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="10">
         <v>50</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="10">
         <v>40</v>
       </c>
     </row>
@@ -997,9 +1029,11 @@
         <v>0.13043478260869565</v>
       </c>
       <c r="H14">
+        <f>H15</f>
         <v>150</v>
       </c>
       <c r="I14">
+        <f>I16</f>
         <v>1150</v>
       </c>
     </row>
@@ -1026,10 +1060,11 @@
         <f>H15 / I15</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="10">
         <v>150</v>
       </c>
       <c r="I15">
+        <f>H16</f>
         <v>0</v>
       </c>
     </row>
@@ -1056,109 +1091,121 @@
         <f>H16 / I16</f>
         <v>0</v>
       </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="I16">
+      <c r="H16" s="10">
+        <v>0</v>
+      </c>
+      <c r="I16" s="10">
         <v>1150</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>21</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C17" t="s">
         <v>18</v>
       </c>
-      <c r="D17" t="s">
-        <v>13</v>
-      </c>
-      <c r="E17" t="s">
-        <v>6</v>
-      </c>
-      <c r="F17" t="s">
-        <v>0</v>
-      </c>
-      <c r="G17" t="e">
+      <c r="D17" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="G17">
         <f>H17 / I17</f>
-        <v>#N/A</v>
+        <v>0.13043478260869565</v>
       </c>
       <c r="H17">
-        <v>0</v>
-      </c>
-      <c r="I17" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+        <f>H18</f>
+        <v>150</v>
+      </c>
+      <c r="I17">
+        <f>I19</f>
+        <v>1150</v>
+      </c>
+      <c r="J17" s="9"/>
+      <c r="K17" s="9"/>
+      <c r="L17" s="9"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>21</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C18" t="s">
         <v>18</v>
       </c>
-      <c r="D18" t="s">
-        <v>8</v>
-      </c>
-      <c r="E18" t="s">
-        <v>6</v>
-      </c>
-      <c r="F18" t="s">
-        <v>4</v>
+      <c r="D18" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>6</v>
       </c>
       <c r="G18" t="e">
-        <f t="shared" ref="G18:G25" si="1">H18 / I18</f>
+        <f>H18 / I18</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H18">
-        <v>0</v>
+      <c r="H18" s="10">
+        <v>150</v>
       </c>
       <c r="I18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+        <f>H19</f>
+        <v>0</v>
+      </c>
+      <c r="J18" s="9"/>
+      <c r="K18" s="9"/>
+      <c r="L18" s="9"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>21</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C19" t="s">
         <v>18</v>
       </c>
-      <c r="D19" t="s">
-        <v>12</v>
-      </c>
-      <c r="E19" t="s">
-        <v>4</v>
-      </c>
-      <c r="F19" t="s">
-        <v>0</v>
-      </c>
-      <c r="G19" t="e">
-        <f t="shared" si="1"/>
-        <v>#N/A</v>
-      </c>
-      <c r="H19">
-        <v>0</v>
-      </c>
-      <c r="I19" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
-        <v>22</v>
+      <c r="D19" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="G19">
+        <f>H19 / I19</f>
+        <v>0</v>
+      </c>
+      <c r="H19" s="10">
+        <v>0</v>
+      </c>
+      <c r="I19" s="10">
+        <v>1150</v>
+      </c>
+      <c r="J19" s="9"/>
+      <c r="K19" s="9"/>
+      <c r="L19" s="9"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C20" t="s">
         <v>18</v>
@@ -1173,257 +1220,942 @@
         <v>7</v>
       </c>
       <c r="G20">
+        <f>H20 / I20</f>
+        <v>9.0909090909090912E-2</v>
+      </c>
+      <c r="H20">
+        <f>H21</f>
+        <v>100</v>
+      </c>
+      <c r="I20">
+        <f>I22</f>
+        <v>1100</v>
+      </c>
+      <c r="J20" s="9"/>
+      <c r="K20" s="9"/>
+      <c r="L20" s="9"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" t="s">
+        <v>18</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="G21" t="e">
+        <f>H21 / I21</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H21" s="10">
+        <v>100</v>
+      </c>
+      <c r="I21">
+        <f>H22</f>
+        <v>0</v>
+      </c>
+      <c r="J21" s="9"/>
+      <c r="K21" s="9"/>
+      <c r="L21" s="9"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" t="s">
+        <v>18</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="G22">
+        <f>H22 / I22</f>
+        <v>0</v>
+      </c>
+      <c r="H22" s="10">
+        <v>0</v>
+      </c>
+      <c r="I22" s="10">
+        <v>1100</v>
+      </c>
+      <c r="J22" s="9"/>
+      <c r="K22" s="9"/>
+      <c r="L22" s="9"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C23" t="s">
+        <v>18</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="G23">
+        <f>H23 / I23</f>
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="H23">
+        <f>H24</f>
+        <v>125</v>
+      </c>
+      <c r="I23">
+        <f>I25</f>
+        <v>1125</v>
+      </c>
+      <c r="J23" s="9"/>
+      <c r="K23" s="9"/>
+      <c r="L23" s="9"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C24" t="s">
+        <v>18</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="G24" t="e">
+        <f>H24 / I24</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H24" s="10">
+        <v>125</v>
+      </c>
+      <c r="I24">
+        <f>H25</f>
+        <v>0</v>
+      </c>
+      <c r="J24" s="9"/>
+      <c r="K24" s="9"/>
+      <c r="L24" s="9"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C25" t="s">
+        <v>18</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="G25">
+        <f>H25 / I25</f>
+        <v>0</v>
+      </c>
+      <c r="H25" s="10">
+        <v>0</v>
+      </c>
+      <c r="I25" s="10">
+        <v>1125</v>
+      </c>
+      <c r="J25" s="9"/>
+      <c r="K25" s="9"/>
+      <c r="L25" s="9"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C26" t="s">
+        <v>18</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="G26">
+        <f>H26 / I26</f>
+        <v>0.13043478260869565</v>
+      </c>
+      <c r="H26">
+        <f>H27</f>
+        <v>150</v>
+      </c>
+      <c r="I26">
+        <f>I28</f>
+        <v>1150</v>
+      </c>
+      <c r="J26" s="9"/>
+      <c r="K26" s="9"/>
+      <c r="L26" s="9"/>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C27" t="s">
+        <v>18</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="G27" t="e">
+        <f>H27 / I27</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H27" s="10">
+        <v>150</v>
+      </c>
+      <c r="I27">
+        <f>H28</f>
+        <v>0</v>
+      </c>
+      <c r="J27" s="9"/>
+      <c r="K27" s="9"/>
+      <c r="L27" s="9"/>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C28" t="s">
+        <v>18</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="G28">
+        <f>H28 / I28</f>
+        <v>0</v>
+      </c>
+      <c r="H28" s="10">
+        <v>0</v>
+      </c>
+      <c r="I28" s="10">
+        <v>1150</v>
+      </c>
+      <c r="J28" s="9"/>
+      <c r="K28" s="9"/>
+      <c r="L28" s="9"/>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C29" t="s">
+        <v>23</v>
+      </c>
+      <c r="D29" t="s">
+        <v>13</v>
+      </c>
+      <c r="E29" t="s">
+        <v>6</v>
+      </c>
+      <c r="F29" t="s">
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <f>H29 / I29</f>
+        <v>6.875</v>
+      </c>
+      <c r="H29">
+        <f>H30</f>
+        <v>275</v>
+      </c>
+      <c r="I29">
+        <f>I31</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C30" t="s">
+        <v>23</v>
+      </c>
+      <c r="D30" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" t="s">
+        <v>6</v>
+      </c>
+      <c r="F30" t="s">
+        <v>4</v>
+      </c>
+      <c r="G30">
+        <f t="shared" ref="G30:G49" si="1">H30 / I30</f>
+        <v>5.5</v>
+      </c>
+      <c r="H30" s="10">
+        <v>275</v>
+      </c>
+      <c r="I30">
+        <f>H31</f>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A31" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C31" t="s">
+        <v>23</v>
+      </c>
+      <c r="D31" t="s">
+        <v>12</v>
+      </c>
+      <c r="E31" t="s">
+        <v>4</v>
+      </c>
+      <c r="F31" t="s">
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <f t="shared" si="1"/>
+        <v>1.25</v>
+      </c>
+      <c r="H31" s="10">
+        <v>50</v>
+      </c>
+      <c r="I31" s="10">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A32" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C32" t="s">
+        <v>23</v>
+      </c>
+      <c r="D32" t="s">
+        <v>13</v>
+      </c>
+      <c r="E32" t="s">
+        <v>6</v>
+      </c>
+      <c r="F32" t="s">
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <f>H32 / I32</f>
+        <v>6.25</v>
+      </c>
+      <c r="H32">
+        <f>H33</f>
+        <v>250</v>
+      </c>
+      <c r="I32">
+        <f>I34</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C33" t="s">
+        <v>23</v>
+      </c>
+      <c r="D33" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" t="s">
+        <v>6</v>
+      </c>
+      <c r="F33" t="s">
+        <v>4</v>
+      </c>
+      <c r="G33">
+        <f t="shared" ref="G33:G34" si="2">H33 / I33</f>
+        <v>5</v>
+      </c>
+      <c r="H33" s="10">
+        <v>250</v>
+      </c>
+      <c r="I33">
+        <f>H34</f>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C34" t="s">
+        <v>23</v>
+      </c>
+      <c r="D34" t="s">
+        <v>12</v>
+      </c>
+      <c r="E34" t="s">
+        <v>4</v>
+      </c>
+      <c r="F34" t="s">
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <f t="shared" si="2"/>
+        <v>1.25</v>
+      </c>
+      <c r="H34" s="10">
+        <v>50</v>
+      </c>
+      <c r="I34" s="10">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C35" t="s">
+        <v>23</v>
+      </c>
+      <c r="D35" t="s">
+        <v>13</v>
+      </c>
+      <c r="E35" t="s">
+        <v>6</v>
+      </c>
+      <c r="F35" t="s">
+        <v>0</v>
+      </c>
+      <c r="G35">
+        <f>H35 / I35</f>
+        <v>6.875</v>
+      </c>
+      <c r="H35">
+        <f>H36</f>
+        <v>275</v>
+      </c>
+      <c r="I35">
+        <f>I37</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C36" t="s">
+        <v>23</v>
+      </c>
+      <c r="D36" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" t="s">
+        <v>6</v>
+      </c>
+      <c r="F36" t="s">
+        <v>4</v>
+      </c>
+      <c r="G36">
+        <f t="shared" ref="G36:G37" si="3">H36 / I36</f>
+        <v>4.583333333333333</v>
+      </c>
+      <c r="H36" s="10">
+        <v>275</v>
+      </c>
+      <c r="I36">
+        <f>H37</f>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C37" t="s">
+        <v>23</v>
+      </c>
+      <c r="D37" t="s">
+        <v>12</v>
+      </c>
+      <c r="E37" t="s">
+        <v>4</v>
+      </c>
+      <c r="F37" t="s">
+        <v>0</v>
+      </c>
+      <c r="G37">
+        <f t="shared" si="3"/>
+        <v>1.5</v>
+      </c>
+      <c r="H37" s="10">
+        <v>60</v>
+      </c>
+      <c r="I37" s="10">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A38" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C38" t="s">
+        <v>23</v>
+      </c>
+      <c r="D38" t="s">
+        <v>13</v>
+      </c>
+      <c r="E38" t="s">
+        <v>6</v>
+      </c>
+      <c r="F38" t="s">
+        <v>0</v>
+      </c>
+      <c r="G38">
+        <f>H38 / I38</f>
+        <v>5</v>
+      </c>
+      <c r="H38">
+        <f>H39</f>
+        <v>300</v>
+      </c>
+      <c r="I38">
+        <f>I40</f>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A39" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C39" t="s">
+        <v>23</v>
+      </c>
+      <c r="D39" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" t="s">
+        <v>6</v>
+      </c>
+      <c r="F39" t="s">
+        <v>4</v>
+      </c>
+      <c r="G39">
+        <f t="shared" ref="G39:G40" si="4">H39 / I39</f>
+        <v>6</v>
+      </c>
+      <c r="H39" s="10">
+        <v>300</v>
+      </c>
+      <c r="I39">
+        <f>H40</f>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A40" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C40" t="s">
+        <v>23</v>
+      </c>
+      <c r="D40" t="s">
+        <v>12</v>
+      </c>
+      <c r="E40" t="s">
+        <v>4</v>
+      </c>
+      <c r="F40" t="s">
+        <v>0</v>
+      </c>
+      <c r="G40">
+        <f t="shared" si="4"/>
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="H40" s="10">
+        <v>50</v>
+      </c>
+      <c r="I40" s="10">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A41" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C41" t="s">
+        <v>23</v>
+      </c>
+      <c r="D41" t="s">
+        <v>13</v>
+      </c>
+      <c r="E41" t="s">
+        <v>6</v>
+      </c>
+      <c r="F41" t="s">
+        <v>0</v>
+      </c>
+      <c r="G41">
+        <f>H41 / I41</f>
+        <v>5</v>
+      </c>
+      <c r="H41">
+        <f>H42</f>
+        <v>300</v>
+      </c>
+      <c r="I41">
+        <f>I43</f>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A42" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C42" t="s">
+        <v>23</v>
+      </c>
+      <c r="D42" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" t="s">
+        <v>6</v>
+      </c>
+      <c r="F42" t="s">
+        <v>4</v>
+      </c>
+      <c r="G42">
+        <f t="shared" ref="G42:G43" si="5">H42 / I42</f>
+        <v>5</v>
+      </c>
+      <c r="H42" s="10">
+        <v>300</v>
+      </c>
+      <c r="I42">
+        <f>H43</f>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A43" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C43" t="s">
+        <v>23</v>
+      </c>
+      <c r="D43" t="s">
+        <v>12</v>
+      </c>
+      <c r="E43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F43" t="s">
+        <v>0</v>
+      </c>
+      <c r="G43">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="H43" s="10">
+        <v>60</v>
+      </c>
+      <c r="I43" s="10">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A44" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C44" t="s">
+        <v>18</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="G44">
         <f t="shared" si="1"/>
         <v>9.9999999999999991E-11</v>
       </c>
-      <c r="H20">
+      <c r="H44">
+        <f>H45</f>
         <v>9.9999999999999995E-8</v>
       </c>
-      <c r="I20">
+      <c r="I44">
+        <f>I46</f>
         <v>1000</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="5" t="s">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A45" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B45" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C21" t="s">
-        <v>18</v>
-      </c>
-      <c r="D21" s="6" t="s">
+      <c r="C45" t="s">
+        <v>18</v>
+      </c>
+      <c r="D45" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="E21" s="6" t="s">
+      <c r="E45" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="F21" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="G21">
+      <c r="F45" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="G45">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="H21">
+      <c r="H45" s="10">
         <v>9.9999999999999995E-8</v>
       </c>
-      <c r="I21">
+      <c r="I45">
+        <f>H46</f>
         <v>9.9999999999999995E-8</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="5" t="s">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A46" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B46" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C22" t="s">
-        <v>18</v>
-      </c>
-      <c r="D22" s="6" t="s">
+      <c r="C46" t="s">
+        <v>18</v>
+      </c>
+      <c r="D46" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E22" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F22" s="6" t="s">
+      <c r="E46" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F46" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G22">
+      <c r="G46">
         <f t="shared" si="1"/>
         <v>9.9999999999999991E-11</v>
       </c>
-      <c r="H22">
+      <c r="H46" s="10">
         <v>9.9999999999999995E-8</v>
       </c>
-      <c r="I22">
+      <c r="I46" s="10">
         <v>1000</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="5" t="s">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A47" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B47" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C47" t="s">
         <v>23</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D47" t="s">
         <v>13</v>
       </c>
-      <c r="E23" t="s">
-        <v>6</v>
-      </c>
-      <c r="F23" t="s">
-        <v>0</v>
-      </c>
-      <c r="G23">
+      <c r="E47" t="s">
+        <v>6</v>
+      </c>
+      <c r="F47" t="s">
+        <v>0</v>
+      </c>
+      <c r="G47">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I23">
+      <c r="H47">
+        <f>H48</f>
+        <v>0</v>
+      </c>
+      <c r="I47">
+        <f>I49</f>
         <v>160</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="5" t="s">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A48" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B48" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C48" t="s">
         <v>23</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D48" t="s">
         <v>8</v>
       </c>
-      <c r="E24" t="s">
-        <v>6</v>
-      </c>
-      <c r="F24" t="s">
+      <c r="E48" t="s">
+        <v>6</v>
+      </c>
+      <c r="F48" t="s">
         <v>4</v>
       </c>
-      <c r="G24" t="e">
+      <c r="G48" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="5" t="s">
+      <c r="H48" s="10"/>
+      <c r="I48">
+        <f>H49</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A49" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B49" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C49" t="s">
         <v>23</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D49" t="s">
         <v>12</v>
       </c>
-      <c r="E25" t="s">
+      <c r="E49" t="s">
         <v>4</v>
       </c>
-      <c r="F25" t="s">
-        <v>0</v>
-      </c>
-      <c r="G25">
+      <c r="F49" t="s">
+        <v>0</v>
+      </c>
+      <c r="G49">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H25">
-        <v>0</v>
-      </c>
-      <c r="I25">
+      <c r="H49" s="10">
+        <v>0</v>
+      </c>
+      <c r="I49" s="10">
         <v>160</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38218A7C-62F8-4E78-8F3B-CF3E2943FA5B}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="41.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="26.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="41.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="26.28515625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" t="s">
-        <v>4</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
